--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$114</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4357" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4395" uniqueCount="709">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T10:00:28+00:00</t>
+    <t>2025-07-07T12:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -683,6 +683,22 @@
   <si>
     <t>Motif de la mesure
 Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
@@ -2529,7 +2545,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP113"/>
+  <dimension ref="A1:AP114"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.2109375" customWidth="true" bestFit="true"/>
@@ -5133,7 +5149,7 @@
         <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5219,46 +5235,44 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>114</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -5306,7 +5320,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5330,7 +5344,7 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5348,7 +5362,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5361,23 +5375,25 @@
         <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O24" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5426,7 +5442,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5438,22 +5454,22 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5461,14 +5477,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5487,17 +5503,17 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5546,7 +5562,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5561,19 +5577,19 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -5581,24 +5597,24 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>82</v>
@@ -5607,18 +5623,18 @@
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5666,7 +5682,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5681,16 +5697,16 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5701,14 +5717,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5718,24 +5734,26 @@
         <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>107</v>
+        <v>248</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5784,31 +5802,31 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>110</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>111</v>
+        <v>254</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5819,21 +5837,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>82</v>
@@ -5845,17 +5863,15 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5892,31 +5908,31 @@
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5939,21 +5955,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5962,19 +5978,19 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>253</v>
+        <v>115</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>254</v>
+        <v>116</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>255</v>
+        <v>117</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6012,31 +6028,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>256</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -6048,7 +6064,7 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -6059,10 +6075,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6085,16 +6101,16 @@
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6120,40 +6136,40 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI30" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AG30" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>105</v>
@@ -6179,10 +6195,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6205,16 +6221,16 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>224</v>
+        <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6240,13 +6256,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -6288,7 +6304,7 @@
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>270</v>
+        <v>196</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6299,10 +6315,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6325,16 +6341,16 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>107</v>
+        <v>229</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6384,7 +6400,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6408,7 +6424,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>196</v>
+        <v>275</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6430,22 +6446,22 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>277</v>
@@ -6456,9 +6472,7 @@
       <c r="N33" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="O33" t="s" s="2">
-        <v>280</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6482,11 +6496,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y33" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z33" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6504,10 +6520,10 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>93</v>
@@ -6519,19 +6535,19 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>286</v>
+        <v>196</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>287</v>
+        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6539,10 +6555,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6553,31 +6569,31 @@
         <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>289</v>
+        <v>173</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6602,35 +6618,35 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AC34" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -6639,19 +6655,19 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6659,14 +6675,12 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>300</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6675,7 +6689,7 @@
         <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>94</v>
@@ -6687,19 +6701,19 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6727,28 +6741,26 @@
         <v>177</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6772,10 +6784,10 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6783,24 +6795,26 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6809,16 +6823,20 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>294</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>108</v>
+        <v>295</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6842,13 +6860,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6866,19 +6884,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>110</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6890,10 +6908,10 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>111</v>
+        <v>302</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6901,21 +6919,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>82</v>
@@ -6927,17 +6945,15 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6974,31 +6990,31 @@
         <v>82</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -7021,46 +7037,44 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>307</v>
+        <v>115</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>308</v>
+        <v>116</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -7096,19 +7110,19 @@
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>311</v>
+        <v>121</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7120,7 +7134,7 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -7129,10 +7143,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>313</v>
+        <v>111</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7143,10 +7157,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7154,31 +7168,35 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>108</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -7226,19 +7244,19 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>110</v>
+        <v>316</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -7247,10 +7265,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>111</v>
+        <v>318</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7261,21 +7279,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -7287,17 +7305,15 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7334,31 +7350,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7381,52 +7397,50 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>320</v>
+        <v>115</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>321</v>
+        <v>116</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>324</v>
+        <v>82</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>82</v>
@@ -7456,31 +7470,31 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>325</v>
+        <v>121</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7489,10 +7503,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7503,10 +7517,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7514,13 +7528,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7529,24 +7543,26 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>82</v>
@@ -7588,7 +7604,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7609,10 +7625,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7623,10 +7639,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7634,13 +7650,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
@@ -7649,24 +7665,24 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7708,7 +7724,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7729,10 +7745,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7743,10 +7759,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7754,13 +7770,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
@@ -7769,27 +7785,27 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>341</v>
+        <v>82</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>82</v>
@@ -7828,7 +7844,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7849,10 +7865,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7863,10 +7879,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7889,19 +7905,17 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>355</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7911,7 +7925,7 @@
         <v>82</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>82</v>
@@ -7950,7 +7964,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7971,10 +7985,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7985,10 +7999,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8011,19 +8025,19 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>360</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -8072,7 +8086,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8093,10 +8107,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8107,24 +8121,24 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
@@ -8133,19 +8147,19 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>289</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8170,13 +8184,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -8194,10 +8208,10 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>93</v>
@@ -8209,62 +8223,66 @@
         <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>380</v>
+        <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>378</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>107</v>
+        <v>294</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>108</v>
+        <v>379</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8288,13 +8306,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8312,10 +8330,10 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>110</v>
+        <v>377</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>93</v>
@@ -8324,44 +8342,44 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>111</v>
+        <v>388</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8373,17 +8391,15 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8420,31 +8436,31 @@
         <v>82</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8467,18 +8483,18 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>81</v>
@@ -8490,23 +8506,21 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>307</v>
+        <v>115</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>308</v>
+        <v>116</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8542,9 +8556,11 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8552,7 +8568,7 @@
         <v>120</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>311</v>
+        <v>121</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8564,7 +8580,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8573,10 +8589,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>313</v>
+        <v>111</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8587,14 +8603,12 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8603,7 +8617,7 @@
         <v>93</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -8618,16 +8632,16 @@
         <v>151</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8664,19 +8678,17 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8697,10 +8709,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8711,18 +8723,20 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="C52" s="2"/>
+      <c r="C52" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
@@ -8734,19 +8748,23 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>108</v>
+        <v>312</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8794,19 +8812,19 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>110</v>
+        <v>316</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8815,10 +8833,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>111</v>
+        <v>318</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8829,21 +8847,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8855,17 +8873,15 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8902,31 +8918,31 @@
         <v>82</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8949,21 +8965,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8972,29 +8988,27 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>320</v>
+        <v>115</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>321</v>
+        <v>116</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>82</v>
@@ -9024,31 +9038,31 @@
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>325</v>
+        <v>121</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -9057,10 +9071,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9071,10 +9085,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9082,7 +9096,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
@@ -9097,24 +9111,26 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>82</v>
@@ -9156,7 +9172,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9177,10 +9193,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9191,10 +9207,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9202,7 +9218,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
@@ -9217,24 +9233,24 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>82</v>
@@ -9276,7 +9292,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9297,10 +9313,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9311,10 +9327,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9322,7 +9338,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
@@ -9337,24 +9353,24 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>82</v>
@@ -9396,7 +9412,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9417,10 +9433,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9431,10 +9447,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9457,19 +9473,17 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>355</v>
+        <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9518,7 +9532,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9539,10 +9553,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9553,10 +9567,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9579,19 +9593,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>107</v>
+        <v>360</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9640,7 +9654,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9661,10 +9675,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9675,10 +9689,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9686,13 +9700,13 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
@@ -9701,19 +9715,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>410</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>411</v>
+        <v>370</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>412</v>
+        <v>371</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>414</v>
+        <v>373</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9762,7 +9776,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>409</v>
+        <v>374</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9777,19 +9791,19 @@
         <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>416</v>
+        <v>375</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>417</v>
+        <v>376</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9797,10 +9811,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9808,13 +9822,13 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
@@ -9823,18 +9837,20 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9882,13 +9898,13 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
@@ -9897,19 +9913,19 @@
         <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>382</v>
+        <v>421</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9917,21 +9933,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9943,20 +9959,18 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>431</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -10004,13 +10018,13 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
@@ -10019,19 +10033,19 @@
         <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>433</v>
+        <v>387</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
@@ -10039,24 +10053,24 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
@@ -10065,19 +10079,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -10126,7 +10140,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10135,25 +10149,25 @@
         <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>444</v>
+        <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -10161,24 +10175,24 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>82</v>
@@ -10187,18 +10201,20 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>129</v>
+        <v>443</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10246,34 +10262,34 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>105</v>
-      </c>
       <c r="AK64" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>82</v>
@@ -10281,10 +10297,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10295,7 +10311,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -10307,18 +10323,18 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>460</v>
-      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10366,13 +10382,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -10381,19 +10397,19 @@
         <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>461</v>
+        <v>82</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>
@@ -10401,10 +10417,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10415,10 +10431,10 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>82</v>
@@ -10427,19 +10443,17 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10476,59 +10490,59 @@
         <v>82</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AC66" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10549,19 +10563,19 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10598,19 +10612,17 @@
         <v>82</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10619,7 +10631,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10628,29 +10640,31 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10662,25 +10676,29 @@
         <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>107</v>
+        <v>471</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>108</v>
+        <v>472</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10728,7 +10746,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>110</v>
+        <v>470</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10737,47 +10755,47 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>111</v>
+        <v>480</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10789,17 +10807,15 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10836,31 +10852,31 @@
         <v>82</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10883,46 +10899,44 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>485</v>
+        <v>114</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>486</v>
+        <v>115</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>487</v>
+        <v>116</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10958,31 +10972,31 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>490</v>
+        <v>121</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10991,10 +11005,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>492</v>
+        <v>111</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -11005,10 +11019,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11016,83 +11030,83 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>173</v>
+        <v>490</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="P71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q71" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="R71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11113,10 +11127,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11127,10 +11141,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11138,37 +11152,39 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I72" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q72" s="2"/>
+      <c r="Q72" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="R72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11188,13 +11204,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -11212,7 +11228,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11233,10 +11249,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11247,10 +11263,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11273,24 +11289,24 @@
         <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>82</v>
@@ -11332,7 +11348,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11341,7 +11357,7 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>519</v>
+        <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -11353,10 +11369,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11367,10 +11383,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11393,26 +11409,24 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q74" s="2"/>
       <c r="R74" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="S74" t="s" s="2">
         <v>82</v>
@@ -11454,7 +11468,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11463,7 +11477,7 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11475,10 +11489,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11489,10 +11503,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11500,7 +11514,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>93</v>
@@ -11512,29 +11526,29 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>289</v>
+        <v>173</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>82</v>
@@ -11552,13 +11566,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11576,7 +11590,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11585,7 +11599,7 @@
         <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>105</v>
@@ -11597,10 +11611,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>196</v>
+        <v>515</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11611,24 +11625,24 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11637,19 +11651,19 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11677,10 +11691,10 @@
         <v>155</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>82</v>
@@ -11698,16 +11712,16 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>105</v>
@@ -11716,31 +11730,31 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>547</v>
+        <v>196</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11759,19 +11773,19 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>551</v>
+        <v>294</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11796,13 +11810,13 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11820,7 +11834,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11838,27 +11852,27 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>82</v>
+        <v>554</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11869,7 +11883,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11881,18 +11895,20 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>289</v>
+        <v>556</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="O78" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="N78" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11916,11 +11932,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>562</v>
+        <v>82</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11938,13 +11956,13 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
@@ -11956,27 +11974,27 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>563</v>
+        <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11990,7 +12008,7 @@
         <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>82</v>
@@ -11999,20 +12017,18 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -12036,11 +12052,11 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>281</v>
+        <v>163</v>
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -12058,7 +12074,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12076,27 +12092,27 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>82</v>
+        <v>571</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12110,7 +12126,7 @@
         <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>82</v>
@@ -12119,16 +12135,20 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>107</v>
+        <v>294</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>108</v>
+        <v>573</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
       </c>
@@ -12152,13 +12172,11 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>82</v>
+        <v>577</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12176,7 +12194,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>110</v>
+        <v>572</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12188,7 +12206,7 @@
         <v>82</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>82</v>
@@ -12197,10 +12215,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>111</v>
+        <v>579</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12211,21 +12229,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12237,17 +12255,15 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12284,31 +12300,31 @@
         <v>82</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -12331,14 +12347,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12354,23 +12370,21 @@
         <v>82</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>307</v>
+        <v>115</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>308</v>
+        <v>116</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12406,19 +12420,19 @@
         <v>82</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>311</v>
+        <v>121</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12430,7 +12444,7 @@
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12439,10 +12453,10 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>313</v>
+        <v>111</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12453,10 +12467,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12467,7 +12481,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12476,19 +12490,23 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>108</v>
+        <v>312</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>313</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12536,19 +12554,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>110</v>
+        <v>316</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12557,10 +12575,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>82</v>
+        <v>317</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>111</v>
+        <v>318</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12571,21 +12589,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12597,17 +12615,15 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12644,31 +12660,31 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12691,21 +12707,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>82</v>
@@ -12714,23 +12730,21 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>320</v>
+        <v>115</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>321</v>
+        <v>116</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12766,31 +12780,31 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>325</v>
+        <v>121</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12799,10 +12813,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>327</v>
+        <v>111</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12813,10 +12827,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12824,7 +12838,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>93</v>
@@ -12839,18 +12853,20 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12898,7 +12914,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12919,10 +12935,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12933,10 +12949,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12944,7 +12960,7 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
         <v>93</v>
@@ -12959,18 +12975,18 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -13018,7 +13034,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13039,10 +13055,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -13053,10 +13069,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13064,7 +13080,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>93</v>
@@ -13079,17 +13095,17 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13138,7 +13154,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13159,10 +13175,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13173,10 +13189,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13199,19 +13215,17 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>355</v>
+        <v>107</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13260,7 +13274,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13281,10 +13295,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13295,10 +13309,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13321,19 +13335,19 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>107</v>
+        <v>360</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13382,7 +13396,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13403,10 +13417,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13417,10 +13431,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13440,21 +13454,23 @@
         <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>587</v>
+        <v>107</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>588</v>
+        <v>370</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>589</v>
+        <v>371</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13502,7 +13518,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>586</v>
+        <v>374</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13520,27 +13536,27 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>592</v>
+        <v>375</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>593</v>
+        <v>376</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>594</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13554,7 +13570,7 @@
         <v>93</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>82</v>
@@ -13563,16 +13579,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13622,7 +13638,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13640,27 +13656,27 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>603</v>
+        <v>599</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13671,10 +13687,10 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>82</v>
@@ -13683,20 +13699,18 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>609</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13744,45 +13758,45 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>610</v>
+        <v>105</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>82</v>
+        <v>608</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13793,7 +13807,7 @@
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13805,16 +13819,20 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>107</v>
+        <v>610</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>108</v>
+        <v>611</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>614</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13862,19 +13880,19 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>110</v>
+        <v>609</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>82</v>
+        <v>615</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -13883,10 +13901,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>82</v>
+        <v>616</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>111</v>
+        <v>617</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13897,21 +13915,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13923,17 +13941,15 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13982,19 +13998,19 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -14017,14 +14033,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>616</v>
+        <v>113</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14037,26 +14053,24 @@
         <v>82</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>617</v>
+        <v>115</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>618</v>
+        <v>116</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O96" t="s" s="2">
-        <v>221</v>
-      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -14104,7 +14118,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>619</v>
+        <v>121</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14128,7 +14142,7 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14146,26 +14160,26 @@
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>621</v>
+        <v>114</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>622</v>
@@ -14173,8 +14187,12 @@
       <c r="M97" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+      <c r="N97" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14222,19 +14240,19 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>624</v>
+        <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -14243,10 +14261,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>626</v>
+        <v>196</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14257,10 +14275,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14283,13 +14301,13 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L98" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14340,7 +14358,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14349,7 +14367,7 @@
         <v>93</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>105</v>
@@ -14361,10 +14379,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14375,10 +14393,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14401,20 +14419,16 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>289</v>
+        <v>626</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N99" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="O99" t="s" s="2">
-        <v>635</v>
-      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14438,13 +14452,13 @@
         <v>82</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>636</v>
+        <v>82</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>82</v>
@@ -14462,7 +14476,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14471,7 +14485,7 @@
         <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>105</v>
@@ -14480,13 +14494,13 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>638</v>
+        <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>548</v>
+        <v>635</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14497,10 +14511,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14511,7 +14525,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14523,19 +14537,19 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14560,13 +14574,13 @@
         <v>82</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>82</v>
@@ -14584,13 +14598,13 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
@@ -14602,13 +14616,13 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14619,10 +14633,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14633,7 +14647,7 @@
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14645,17 +14659,19 @@
         <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14680,13 +14696,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>82</v>
+        <v>650</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14704,13 +14720,13 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
@@ -14722,13 +14738,13 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>82</v>
+        <v>644</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>652</v>
+        <v>553</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14739,10 +14755,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14765,7 +14781,7 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>107</v>
+        <v>653</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>654</v>
@@ -14774,7 +14790,9 @@
         <v>655</v>
       </c>
       <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+      <c r="O102" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
       </c>
@@ -14822,7 +14840,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14843,10 +14861,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14857,10 +14875,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14871,7 +14889,7 @@
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
@@ -14880,10 +14898,10 @@
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>658</v>
+        <v>107</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>659</v>
@@ -14891,9 +14909,7 @@
       <c r="M103" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="N103" t="s" s="2">
-        <v>661</v>
-      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14942,13 +14958,13 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
@@ -14963,10 +14979,10 @@
         <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>662</v>
+        <v>630</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14977,10 +14993,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15003,16 +15019,16 @@
         <v>94</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>668</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -15062,7 +15078,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15083,10 +15099,10 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15097,10 +15113,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15114,7 +15130,7 @@
         <v>81</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>82</v>
@@ -15123,20 +15139,18 @@
         <v>94</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>605</v>
+        <v>670</v>
       </c>
       <c r="L105" t="s" s="2">
         <v>671</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O105" t="s" s="2">
         <v>673</v>
       </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -15184,7 +15198,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15196,19 +15210,19 @@
         <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AN105" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15219,10 +15233,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15233,28 +15247,32 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>107</v>
+        <v>610</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>108</v>
+        <v>676</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>676</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>678</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15302,19 +15320,19 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>110</v>
+        <v>675</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>82</v>
+        <v>679</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>82</v>
@@ -15323,10 +15341,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>82</v>
+        <v>680</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>111</v>
+        <v>681</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15337,21 +15355,21 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>82</v>
@@ -15363,17 +15381,15 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15422,19 +15438,19 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>82</v>
@@ -15457,14 +15473,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>616</v>
+        <v>113</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15477,26 +15493,24 @@
         <v>82</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>617</v>
+        <v>115</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>618</v>
+        <v>116</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O108" t="s" s="2">
-        <v>221</v>
-      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15544,7 +15558,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>619</v>
+        <v>121</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15568,7 +15582,7 @@
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15579,45 +15593,45 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I109" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>289</v>
+        <v>114</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>681</v>
+        <v>622</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>682</v>
+        <v>623</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>683</v>
+        <v>117</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>684</v>
+        <v>226</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15642,13 +15656,13 @@
         <v>82</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>379</v>
+        <v>82</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>82</v>
@@ -15666,34 +15680,34 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>680</v>
+        <v>624</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>685</v>
+        <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>383</v>
+        <v>196</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>384</v>
+        <v>82</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>82</v>
@@ -15701,10 +15715,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15712,7 +15726,7 @@
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>93</v>
@@ -15727,19 +15741,19 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
@@ -15767,10 +15781,10 @@
         <v>155</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>691</v>
+        <v>383</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>692</v>
+        <v>384</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>82</v>
@@ -15788,16 +15802,16 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>693</v>
+        <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>105</v>
@@ -15806,27 +15820,27 @@
         <v>82</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>474</v>
+        <v>387</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>475</v>
+        <v>388</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15846,22 +15860,22 @@
         <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>289</v>
+        <v>692</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>533</v>
+        <v>474</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15889,10 +15903,10 @@
         <v>155</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>534</v>
+        <v>696</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>535</v>
+        <v>697</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>82</v>
@@ -15910,7 +15924,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15919,7 +15933,7 @@
         <v>93</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>105</v>
@@ -15928,19 +15942,19 @@
         <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>82</v>
+        <v>699</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>196</v>
+        <v>479</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>537</v>
+        <v>480</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
     </row>
     <row r="112" hidden="true">
@@ -15952,17 +15966,17 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>82</v>
@@ -15971,19 +15985,19 @@
         <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>540</v>
+        <v>701</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>541</v>
+        <v>702</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>542</v>
+        <v>703</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
@@ -16011,10 +16025,10 @@
         <v>155</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>82</v>
@@ -16038,10 +16052,10 @@
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>82</v>
+        <v>704</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>105</v>
@@ -16050,31 +16064,31 @@
         <v>82</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>546</v>
+        <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>547</v>
+        <v>196</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16093,19 +16107,19 @@
         <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>702</v>
+        <v>545</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>703</v>
+        <v>546</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>608</v>
+        <v>547</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>609</v>
+        <v>548</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16130,13 +16144,13 @@
         <v>82</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16154,7 +16168,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16172,23 +16186,145 @@
         <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>611</v>
+        <v>552</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>612</v>
+        <v>553</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP113" t="s" s="2">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP114" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP113">
+  <autoFilter ref="A1:AP114">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16198,7 +16334,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI112">
+  <conditionalFormatting sqref="A2:AI113">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T12:38:35+00:00</t>
+    <t>2025-07-07T15:58:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1306,7 +1306,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1360,7 +1360,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
 </t>
   </si>
   <si>
@@ -1455,7 +1455,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2558,7 +2558,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="179.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
+++ b/nr-create-ruleset-refacto/ig/StructureDefinition-mesures-fr-observation-oxygen-sat.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:58:33+00:00</t>
+    <t>2025-07-07T16:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
